--- a/analysis/paper tables and figures/table 5 usability comparison by rank order.xlsx
+++ b/analysis/paper tables and figures/table 5 usability comparison by rank order.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\misc\GitHub\FuzzDojo\analysis\paper tables and figures\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SW\Desktop\1\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="12460" tabRatio="500"/>
+    <workbookView xWindow="-111" yWindow="-111" windowWidth="23263" windowHeight="12463" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Survey-data" sheetId="9" r:id="rId1"/>
@@ -914,12 +914,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P949"/>
-  <sheetFormatPr defaultRowHeight="12.5"/>
+  <sheetFormatPr defaultRowHeight="12.45"/>
   <cols>
-    <col min="1" max="1" width="14.36328125" style="7" customWidth="1"/>
-    <col min="2" max="2" width="9.81640625" style="1" customWidth="1"/>
-    <col min="3" max="16" width="8.81640625" style="1"/>
-    <col min="17" max="17" width="10.81640625" customWidth="1"/>
+    <col min="1" max="1" width="14.3828125" style="7" customWidth="1"/>
+    <col min="2" max="2" width="9.84375" style="1" customWidth="1"/>
+    <col min="3" max="16" width="8.84375" style="1"/>
+    <col min="17" max="17" width="10.84375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -939,7 +939,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="409.6" hidden="1" thickBot="1">
+    <row r="3" spans="1:16">
+      <c r="A3" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="385.75" hidden="1" thickBot="1">
       <c r="A4" s="8"/>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -987,7 +992,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="63" thickBot="1">
+    <row r="5" spans="1:16" ht="62.6" thickBot="1">
       <c r="A5" s="6" t="s">
         <v>20</v>
       </c>
@@ -1037,7 +1042,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="13" thickBot="1">
+    <row r="6" spans="1:16" ht="12.9" thickBot="1">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -1087,7 +1092,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="13" thickBot="1">
+    <row r="7" spans="1:16" ht="12.9" thickBot="1">
       <c r="A7" s="4">
         <f>A6+1</f>
         <v>2</v>
@@ -1138,7 +1143,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="13" thickBot="1">
+    <row r="8" spans="1:16" ht="12.9" thickBot="1">
       <c r="A8" s="4">
         <f t="shared" ref="A8:A25" si="0">A7+1</f>
         <v>3</v>
@@ -1189,7 +1194,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="13" thickBot="1">
+    <row r="9" spans="1:16" ht="12.9" thickBot="1">
       <c r="A9" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1240,7 +1245,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="13" thickBot="1">
+    <row r="10" spans="1:16" ht="12.9" thickBot="1">
       <c r="A10" s="4">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1291,7 +1296,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="13" thickBot="1">
+    <row r="11" spans="1:16" ht="12.9" thickBot="1">
       <c r="A11" s="4">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1342,7 +1347,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="13" thickBot="1">
+    <row r="12" spans="1:16" ht="12.9" thickBot="1">
       <c r="A12" s="4">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1393,7 +1398,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="13" thickBot="1">
+    <row r="13" spans="1:16" ht="12.9" thickBot="1">
       <c r="A13" s="4">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1444,7 +1449,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="13" thickBot="1">
+    <row r="14" spans="1:16" ht="12.9" thickBot="1">
       <c r="A14" s="4">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1495,7 +1500,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="13" thickBot="1">
+    <row r="15" spans="1:16" ht="12.9" thickBot="1">
       <c r="A15" s="4">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1546,7 +1551,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="13" thickBot="1">
+    <row r="16" spans="1:16" ht="12.9" thickBot="1">
       <c r="A16" s="4">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1597,7 +1602,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="13" thickBot="1">
+    <row r="17" spans="1:16" ht="12.9" thickBot="1">
       <c r="A17" s="4">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1648,7 +1653,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="13" thickBot="1">
+    <row r="18" spans="1:16" ht="12.9" thickBot="1">
       <c r="A18" s="4">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1699,7 +1704,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="13" thickBot="1">
+    <row r="19" spans="1:16" ht="12.9" thickBot="1">
       <c r="A19" s="4">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1750,7 +1755,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="13" thickBot="1">
+    <row r="20" spans="1:16" ht="12.9" thickBot="1">
       <c r="A20" s="4">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1801,7 +1806,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="13" thickBot="1">
+    <row r="21" spans="1:16" ht="12.9" thickBot="1">
       <c r="A21" s="4">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1852,7 +1857,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="13" thickBot="1">
+    <row r="22" spans="1:16" ht="12.9" thickBot="1">
       <c r="A22" s="4">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -1903,7 +1908,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="13" thickBot="1">
+    <row r="23" spans="1:16" ht="12.9" thickBot="1">
       <c r="A23" s="4">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -1954,7 +1959,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="13" thickBot="1">
+    <row r="24" spans="1:16" ht="12.9" thickBot="1">
       <c r="A24" s="4">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -2005,7 +2010,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="13" thickBot="1">
+    <row r="25" spans="1:16" ht="12.9" thickBot="1">
       <c r="A25" s="4">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -2056,7 +2061,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="13" thickBot="1">
+    <row r="26" spans="1:16" ht="12.9" thickBot="1">
       <c r="A26" s="4">
         <v>21</v>
       </c>
@@ -2106,7 +2111,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="13" thickBot="1">
+    <row r="27" spans="1:16" ht="12.9" thickBot="1">
       <c r="A27" s="4"/>
       <c r="B27"/>
       <c r="C27"/>
@@ -2860,7 +2865,7 @@
       <c r="O45"/>
       <c r="P45"/>
     </row>
-    <row r="46" spans="1:16" ht="14.5">
+    <row r="46" spans="1:16" ht="14.6">
       <c r="A46" s="25"/>
       <c r="B46" s="15" t="s">
         <v>72</v>
@@ -2889,7 +2894,7 @@
       <c r="O46"/>
       <c r="P46"/>
     </row>
-    <row r="47" spans="1:16" ht="14.5">
+    <row r="47" spans="1:16" ht="14.6">
       <c r="A47" s="25"/>
       <c r="B47" s="15" t="s">
         <v>67</v>
@@ -2918,7 +2923,7 @@
       <c r="O47"/>
       <c r="P47"/>
     </row>
-    <row r="48" spans="1:16" ht="14.5">
+    <row r="48" spans="1:16" ht="14.6">
       <c r="A48" s="25"/>
       <c r="B48" s="15" t="s">
         <v>73</v>
@@ -2947,7 +2952,7 @@
       <c r="O48"/>
       <c r="P48"/>
     </row>
-    <row r="49" spans="1:16" ht="14.5">
+    <row r="49" spans="1:16" ht="14.6">
       <c r="A49" s="25"/>
       <c r="B49" s="15" t="s">
         <v>69</v>
@@ -2976,7 +2981,7 @@
       <c r="O49"/>
       <c r="P49"/>
     </row>
-    <row r="50" spans="1:16" ht="14.5">
+    <row r="50" spans="1:16" ht="14.6">
       <c r="A50" s="25"/>
       <c r="B50" s="15" t="s">
         <v>74</v>
@@ -3005,7 +3010,7 @@
       <c r="O50"/>
       <c r="P50"/>
     </row>
-    <row r="51" spans="1:16" ht="14.5">
+    <row r="51" spans="1:16" ht="14.6">
       <c r="A51" s="25"/>
       <c r="B51" s="15" t="s">
         <v>64</v>
@@ -3034,7 +3039,7 @@
       <c r="O51"/>
       <c r="P51"/>
     </row>
-    <row r="52" spans="1:16" ht="14.5">
+    <row r="52" spans="1:16" ht="14.6">
       <c r="A52" s="25"/>
       <c r="B52" s="15" t="s">
         <v>75</v>
@@ -3063,7 +3068,7 @@
       <c r="O52"/>
       <c r="P52"/>
     </row>
-    <row r="53" spans="1:16" ht="14.5">
+    <row r="53" spans="1:16" ht="14.6">
       <c r="A53" s="25"/>
       <c r="B53" s="15" t="s">
         <v>56</v>
@@ -3092,7 +3097,7 @@
       <c r="O53"/>
       <c r="P53"/>
     </row>
-    <row r="54" spans="1:16" ht="14.5">
+    <row r="54" spans="1:16" ht="14.6">
       <c r="A54" s="25"/>
       <c r="B54" s="15" t="s">
         <v>65</v>
@@ -3121,7 +3126,7 @@
       <c r="O54"/>
       <c r="P54"/>
     </row>
-    <row r="55" spans="1:16" ht="14.5">
+    <row r="55" spans="1:16" ht="14.6">
       <c r="A55" s="25"/>
       <c r="B55" s="15" t="s">
         <v>68</v>
@@ -3150,7 +3155,7 @@
       <c r="O55"/>
       <c r="P55"/>
     </row>
-    <row r="56" spans="1:16" ht="14.5">
+    <row r="56" spans="1:16" ht="14.6">
       <c r="A56" s="25"/>
       <c r="B56" s="15" t="s">
         <v>70</v>
@@ -3179,7 +3184,7 @@
       <c r="O56"/>
       <c r="P56"/>
     </row>
-    <row r="57" spans="1:16" ht="14.5">
+    <row r="57" spans="1:16" ht="14.6">
       <c r="A57" s="25"/>
       <c r="B57" s="15" t="s">
         <v>71</v>
@@ -3208,7 +3213,7 @@
       <c r="O57"/>
       <c r="P57"/>
     </row>
-    <row r="58" spans="1:16" ht="14.5">
+    <row r="58" spans="1:16" ht="14.6">
       <c r="A58" s="25"/>
       <c r="B58" s="15" t="s">
         <v>63</v>
@@ -3237,7 +3242,7 @@
       <c r="O58"/>
       <c r="P58"/>
     </row>
-    <row r="59" spans="1:16" ht="14.5">
+    <row r="59" spans="1:16" ht="14.6">
       <c r="A59" s="25"/>
       <c r="B59" s="15" t="s">
         <v>62</v>
@@ -3266,7 +3271,7 @@
       <c r="O59"/>
       <c r="P59"/>
     </row>
-    <row r="60" spans="1:16" ht="14.5">
+    <row r="60" spans="1:16" ht="14.6">
       <c r="A60" s="25"/>
       <c r="B60" s="15" t="s">
         <v>66</v>
@@ -3314,11 +3319,11 @@
       <c r="B66" s="11"/>
       <c r="D66" s="13"/>
     </row>
-    <row r="67" spans="2:10" ht="14.5">
+    <row r="67" spans="2:10" ht="14.6">
       <c r="B67" s="11"/>
       <c r="J67" s="14"/>
     </row>
-    <row r="68" spans="2:10" ht="14.5">
+    <row r="68" spans="2:10" ht="14.6">
       <c r="B68" s="11"/>
       <c r="J68" s="14"/>
     </row>
